--- a/MBF04S.xlsx
+++ b/MBF04S.xlsx
@@ -700,7 +700,7 @@
     <t>20138474</t>
   </si>
   <si>
-    <t>VIDORAN 5  MADU 900G</t>
+    <t>VDRN XMRT5+ MDU 900G</t>
   </si>
   <si>
     <t>20135200</t>
@@ -1006,13 +1006,13 @@
     <t>20065379</t>
   </si>
   <si>
-    <t>SGM SOYA1+ VANL 700G</t>
+    <t>SGM SOYA1+VNL  700 G</t>
   </si>
   <si>
     <t>20071686</t>
   </si>
   <si>
-    <t>SGM SOYA1+ MADU 700G</t>
+    <t>SGM SOYA1+MD  700 G</t>
   </si>
   <si>
     <t>20005712</t>
@@ -1033,13 +1033,13 @@
     <t>10009493</t>
   </si>
   <si>
-    <t>DNCOW FRTGO COK 390G</t>
+    <t>DNCOW FRTG CKL 390 G</t>
   </si>
   <si>
     <t>10006259</t>
   </si>
   <si>
-    <t>DNCOW FRTGO ENR 780G</t>
+    <t>DANCOW FRTG 780 G</t>
   </si>
   <si>
     <t>10006260</t>
@@ -1051,7 +1051,7 @@
     <t>10006258</t>
   </si>
   <si>
-    <t>DNCOWFRTGO F.CR 780G</t>
+    <t>DNCOW FRTG F.C 780 G</t>
   </si>
   <si>
     <t>10006262</t>
@@ -1123,13 +1123,13 @@
     <t>20113345</t>
   </si>
   <si>
-    <t>LACTOGRW PRO1+VAN350</t>
+    <t>LCTGRW PRO1+VN 350 G</t>
   </si>
   <si>
     <t>20035629</t>
   </si>
   <si>
-    <t>BEBELAC 1+VNL BOX350</t>
+    <t>BEBELAC1+ VN B 350 G</t>
   </si>
   <si>
     <t>25</t>
@@ -1150,13 +1150,13 @@
     <t>10025848</t>
   </si>
   <si>
-    <t>NTRILON 3 RYL VAN400</t>
+    <t>NTRILON R 3 VN 400 G</t>
   </si>
   <si>
     <t>20055287</t>
   </si>
   <si>
-    <t>LACTOGRW PRO1+MDU350</t>
+    <t>LCTGRW PRO1+MD 350 G</t>
   </si>
   <si>
     <t>20017965</t>
@@ -1228,7 +1228,7 @@
     <t>20035631</t>
   </si>
   <si>
-    <t>BEBELAC1+ MDU BOX350</t>
+    <t>BEBELAC1+ MD B 350 G</t>
   </si>
   <si>
     <t>20136285</t>

--- a/MBF04S.xlsx
+++ b/MBF04S.xlsx
@@ -934,13 +934,13 @@
     <t>20074147</t>
   </si>
   <si>
-    <t>SGM EKSPL1+ MADU 600</t>
+    <t>SGM EKSPL1+ MD 600 G</t>
   </si>
   <si>
     <t>20077508</t>
   </si>
   <si>
-    <t>SGM EKSPL1+ VAN 600G</t>
+    <t>SGM EKSPL1+ VN 600 G</t>
   </si>
   <si>
     <t>20040294</t>
@@ -979,7 +979,7 @@
     <t>20066494</t>
   </si>
   <si>
-    <t>SGM EKSPL5+ MADU 900</t>
+    <t>SGM EKSPL5+ MD 900 G</t>
   </si>
   <si>
     <t>10005315</t>
@@ -1045,7 +1045,7 @@
     <t>10006260</t>
   </si>
   <si>
-    <t>DNCOW FRTGO COK 780</t>
+    <t>DNCOW FRGO CKT 780 G</t>
   </si>
   <si>
     <t>10006258</t>
@@ -1243,25 +1243,25 @@
     <t>20122291</t>
   </si>
   <si>
-    <t>BEBELAC1+ MDU BOX600</t>
+    <t>BEBELAC1+ M BX 600 G</t>
   </si>
   <si>
     <t>20122288</t>
   </si>
   <si>
-    <t>BEBELAC1+ VAN BOX600</t>
+    <t>BEBELAC1+ V BX 600 G</t>
   </si>
   <si>
     <t>20069146</t>
   </si>
   <si>
-    <t>BEBELAC1+ MDU BX1000</t>
+    <t>BEBELAC1+ MD BX 1 KG</t>
   </si>
   <si>
     <t>20069147</t>
   </si>
   <si>
-    <t>BEBELAC1+ VNL BX1000</t>
+    <t>BEBELAC1+ VN BX 1 KG</t>
   </si>
   <si>
     <t>20139959</t>

--- a/MBF04S.xlsx
+++ b/MBF04S.xlsx
@@ -556,13 +556,13 @@
     <t>20027850</t>
   </si>
   <si>
-    <t>ZEE VNILA TWST 340G</t>
+    <t>ZEE SS VNL TWS 340 G</t>
   </si>
   <si>
     <t>20027848</t>
   </si>
   <si>
-    <t>ZEE SWIZZ CHO 340G</t>
+    <t>ZEE SS SWZ CHO 340 G</t>
   </si>
   <si>
     <t>10033006</t>
@@ -586,7 +586,7 @@
     <t>10000578</t>
   </si>
   <si>
-    <t>DIABETASOL VNL.170GR</t>
+    <t>DIABETASOL VNL 170 G</t>
   </si>
   <si>
     <t>20142907</t>
@@ -640,19 +640,19 @@
     <t>20117983</t>
   </si>
   <si>
-    <t>VIDORAN XM5+ COKL700</t>
+    <t>VDORAN X5+ COK 700 G</t>
   </si>
   <si>
     <t>20098371</t>
   </si>
   <si>
-    <t>VDORAN SUSU MADU 325</t>
+    <t>VDORAN X3+ MDU 350 G</t>
   </si>
   <si>
     <t>20098369</t>
   </si>
   <si>
-    <t>VDORAN XMRT3+ VAN350</t>
+    <t>VDORAN X3+ VAN 350 G</t>
   </si>
   <si>
     <t>20101825</t>
@@ -721,13 +721,13 @@
     <t>20117985</t>
   </si>
   <si>
-    <t>VIDORAN XM5+ MADU700</t>
+    <t>VDORAN X5+ MDU 700 G</t>
   </si>
   <si>
     <t>20142954</t>
   </si>
   <si>
-    <t>VIDORAN 5+VAN 700G</t>
+    <t>VDORAN X5+ VAN 700 G</t>
   </si>
   <si>
     <t>20125788</t>
@@ -760,7 +760,7 @@
     <t>10025373</t>
   </si>
   <si>
-    <t>ENTRASOL GOLD VAN170</t>
+    <t>ENTRSL GOLD VA 170 G</t>
   </si>
   <si>
     <t>20021571</t>
@@ -772,19 +772,19 @@
     <t>10020147</t>
   </si>
   <si>
-    <t>ANLENE GOLD CKLT 230</t>
+    <t>ANLENE GOLD CO 230 G</t>
   </si>
   <si>
     <t>10008064</t>
   </si>
   <si>
-    <t>ANLENE GOLD ORG240G</t>
+    <t>ANLENE GOLD OR 240 G</t>
   </si>
   <si>
     <t>10012172</t>
   </si>
   <si>
-    <t>ANLENE GOLD VNLA 230</t>
+    <t>ANLENE GOLD VA 230 G</t>
   </si>
   <si>
     <t>10003653</t>
@@ -799,7 +799,7 @@
     <t>20014399</t>
   </si>
   <si>
-    <t>MORINAGA CK3 VAN 780</t>
+    <t>MRINAGA CK3 VA 780 G</t>
   </si>
   <si>
     <t>10005241</t>
@@ -811,25 +811,25 @@
     <t>10008314</t>
   </si>
   <si>
-    <t>MORINAGA CK VNLA 190</t>
+    <t>MRINAGA CK VNL 190 G</t>
   </si>
   <si>
     <t>10008316</t>
   </si>
   <si>
-    <t>MORINAGA CK MADU 190</t>
+    <t>MRINAGA CK MD 190 G</t>
   </si>
   <si>
     <t>10010874</t>
   </si>
   <si>
-    <t>DNCOW 1+ MDU BOX 120</t>
+    <t>DNCOW1+ MDU BX 120 G</t>
   </si>
   <si>
     <t>10005338</t>
   </si>
   <si>
-    <t>DNCOW FRTGO BOX 195G</t>
+    <t>DNCOW FRTG BX 195 G</t>
   </si>
   <si>
     <t>10026038</t>
@@ -874,7 +874,7 @@
     <t>10009494</t>
   </si>
   <si>
-    <t>DANCOW FORTIGRO 390G</t>
+    <t>DNCOW FORTIGRO 390 G</t>
   </si>
   <si>
     <t>20040340</t>
@@ -1027,7 +1027,7 @@
     <t>10009495</t>
   </si>
   <si>
-    <t>DNCW FRTG FL.CRM 390</t>
+    <t>DNCOW FRTG F.C 390 G</t>
   </si>
   <si>
     <t>10009493</t>
@@ -1057,7 +1057,7 @@
     <t>10006262</t>
   </si>
   <si>
-    <t>DNCOW 1+ MDU BOX 750</t>
+    <t>DNCOW1+ MDU BX 750 G</t>
   </si>
   <si>
     <t>23</t>
@@ -1066,31 +1066,31 @@
     <t>10015652</t>
   </si>
   <si>
-    <t>DNCOW 1+ VAN BOX 750</t>
+    <t>DNCOW1+ VAN BX 750 G</t>
   </si>
   <si>
     <t>10013035</t>
   </si>
   <si>
-    <t>DNCOW 3+ MDU BOX 750</t>
+    <t>DNCOW3+ MDU BX 750 G</t>
   </si>
   <si>
     <t>10015650</t>
   </si>
   <si>
-    <t>DNCOW 3+ VAN BOX 750</t>
+    <t>DNCOW3+ VAN BX 750 G</t>
   </si>
   <si>
     <t>10023780</t>
   </si>
   <si>
-    <t>DNCOW 5+ MDU BOX 750</t>
+    <t>DNCOW5+ MDU BX 750 G</t>
   </si>
   <si>
     <t>10009496</t>
   </si>
   <si>
-    <t>DNCOW 1+ MDU BOX 350</t>
+    <t>DNCOW1+ MDU BX 350 G</t>
   </si>
   <si>
     <t>24</t>
@@ -1099,19 +1099,19 @@
     <t>10015653</t>
   </si>
   <si>
-    <t>DNCOW 1+ VAN BOX 350</t>
+    <t>DNCOW1+ VAN BX 350 G</t>
   </si>
   <si>
     <t>10012967</t>
   </si>
   <si>
-    <t>DNCOW 3+ MDU BOX 350</t>
+    <t>DNCOW3+ MDU BX 350 G</t>
   </si>
   <si>
     <t>10015651</t>
   </si>
   <si>
-    <t>DNCOW3+ VAN BOX  350</t>
+    <t>DNCOW3+ VAN BX 350 G</t>
   </si>
   <si>
     <t>20017679</t>

--- a/MBF04S.xlsx
+++ b/MBF04S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="432">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1212" uniqueCount="438">
   <si>
     <t/>
   </si>
@@ -115,7 +115,7 @@
     <t>20094283</t>
   </si>
   <si>
-    <t>INDOMILK KM PTH 535G</t>
+    <t>INDMLK KM P PH 535 G</t>
   </si>
   <si>
     <t>10</t>
@@ -124,7 +124,7 @@
     <t>20120855</t>
   </si>
   <si>
-    <t>INDOMILK SWIS CHO535</t>
+    <t>INDMLK KM SC P 535 G</t>
   </si>
   <si>
     <t>11</t>
@@ -247,262 +247,1036 @@
     <t>PROMNA PSTA BLOGNESE</t>
   </si>
   <si>
+    <t>20067680</t>
+  </si>
+  <si>
+    <t>PRMNA PUDNG STRW 100</t>
+  </si>
+  <si>
+    <t>20113322</t>
+  </si>
+  <si>
+    <t>PROMINA PASTA M&amp;C 70</t>
+  </si>
+  <si>
+    <t>20126004</t>
+  </si>
+  <si>
+    <t>PROMINA PASTA CCS 60</t>
+  </si>
+  <si>
+    <t>20126003</t>
+  </si>
+  <si>
+    <t>PRMNA MI BT AYM KP75</t>
+  </si>
+  <si>
+    <t>10025325</t>
+  </si>
+  <si>
+    <t>PRMNA SUPMI AYM SY81</t>
+  </si>
+  <si>
+    <t>10025326</t>
+  </si>
+  <si>
+    <t>PRMN SUPMI DG&amp;SYR 84</t>
+  </si>
+  <si>
+    <t>20135120</t>
+  </si>
+  <si>
+    <t>PRMNA SFTCRN BUTER15</t>
+  </si>
+  <si>
+    <t>20134695</t>
+  </si>
+  <si>
+    <t>PRMNA CRCKR BRRIES20</t>
+  </si>
+  <si>
+    <t>20094437</t>
+  </si>
+  <si>
+    <t>PROMINA CRUNCHIES 20</t>
+  </si>
+  <si>
+    <t>20129287</t>
+  </si>
+  <si>
+    <t>PRMINA CRN SEAWED 20</t>
+  </si>
+  <si>
+    <t>20129288</t>
+  </si>
+  <si>
+    <t>PRMINA CRN CHKN.BR20</t>
+  </si>
+  <si>
+    <t>20136087</t>
+  </si>
+  <si>
+    <t>PRMNA SFTCRN STRWB15</t>
+  </si>
+  <si>
+    <t>20141387</t>
+  </si>
+  <si>
+    <t>PROMINA MC CHO.AL 42</t>
+  </si>
+  <si>
+    <t>20141376</t>
+  </si>
+  <si>
+    <t>PROMINA MC BL.CHS 42</t>
+  </si>
+  <si>
+    <t>20133324</t>
+  </si>
+  <si>
+    <t>PRMINA CRCKR BRCLI20</t>
+  </si>
+  <si>
+    <t>20144401</t>
+  </si>
+  <si>
+    <t>MLTGRN ROL BLBRY 20G</t>
+  </si>
+  <si>
+    <t>20144400</t>
+  </si>
+  <si>
+    <t>MLTGRN ROL CKLT 20G</t>
+  </si>
+  <si>
+    <t>20077368</t>
+  </si>
+  <si>
+    <t>PRMINA PUFF BNANA 15</t>
+  </si>
+  <si>
+    <t>20077369</t>
+  </si>
+  <si>
+    <t>PRMINA PUFF BLUBR 15</t>
+  </si>
+  <si>
+    <t>20092042</t>
+  </si>
+  <si>
+    <t>PRMINA PUFF STRWAP15</t>
+  </si>
+  <si>
+    <t>20138373</t>
+  </si>
+  <si>
+    <t>PROMINA PUFF WGYU 15</t>
+  </si>
+  <si>
+    <t>20139421</t>
+  </si>
+  <si>
+    <t>PRMINA YGR MLT SRW 8</t>
+  </si>
+  <si>
+    <t>20139431</t>
+  </si>
+  <si>
+    <t>PRMINA YGR MLT MLK 8</t>
+  </si>
+  <si>
+    <t>20138655</t>
+  </si>
+  <si>
+    <t>MILNA PUFFS SWEED 13</t>
+  </si>
+  <si>
+    <t>20109115</t>
+  </si>
+  <si>
+    <t>MLNA PUFFS ORG BNN15</t>
+  </si>
+  <si>
+    <t>20103062</t>
+  </si>
+  <si>
+    <t>MLNA PUFFS ORG AMB15</t>
+  </si>
+  <si>
+    <t>20103061</t>
+  </si>
+  <si>
+    <t>MLNA PUFFS ORG CHS15</t>
+  </si>
+  <si>
+    <t>20027865</t>
+  </si>
+  <si>
+    <t>MILNA SUP AYM JG 100</t>
+  </si>
+  <si>
+    <t>20027867</t>
+  </si>
+  <si>
+    <t>MILNA ATI AYM BYM120</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>20122054</t>
+  </si>
+  <si>
+    <t>MLNA BBR SLMN CB 100</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>20137013</t>
+  </si>
+  <si>
+    <t>MILNA CRNCH CHSE 20G</t>
+  </si>
+  <si>
+    <t>20138656</t>
+  </si>
+  <si>
+    <t>MILNA CRN BERIES 20</t>
+  </si>
+  <si>
+    <t>20115159</t>
+  </si>
+  <si>
+    <t>MLNA RC.CRAC BNANA20</t>
+  </si>
+  <si>
+    <t>20115158</t>
+  </si>
+  <si>
+    <t>MLNA RC.CRACK SPC 20</t>
+  </si>
+  <si>
+    <t>20092863</t>
+  </si>
+  <si>
+    <t>YB BABY CRCK STRW 25</t>
+  </si>
+  <si>
+    <t>20080924</t>
+  </si>
+  <si>
+    <t>YB BABY CRACK BNN 25</t>
+  </si>
+  <si>
+    <t>20143371</t>
+  </si>
+  <si>
+    <t>MNDE BRMN CKS TMGO40</t>
+  </si>
+  <si>
+    <t>20143372</t>
+  </si>
+  <si>
+    <t>MNDE BRMN CKS BNNA40</t>
+  </si>
+  <si>
+    <t>20142228</t>
+  </si>
+  <si>
+    <t>CAP ENAK CHOCO 535G</t>
+  </si>
+  <si>
+    <t>20125783</t>
+  </si>
+  <si>
+    <t>CAP/ENAK KKM PTH 535</t>
+  </si>
+  <si>
+    <t>20140647</t>
+  </si>
+  <si>
+    <t>ENAK K/MNS COKLAT260</t>
+  </si>
+  <si>
+    <t>20140646</t>
+  </si>
+  <si>
+    <t>ENAK K/MNS PUTIH 260</t>
+  </si>
+  <si>
+    <t>20143301</t>
+  </si>
+  <si>
+    <t>INDMLK CRM MTCHA 260</t>
+  </si>
+  <si>
+    <t>10000255</t>
+  </si>
+  <si>
+    <t>FF GOLD SKM PTH 370G</t>
+  </si>
+  <si>
+    <t>20002313</t>
+  </si>
+  <si>
+    <t>FF KRM MNS OMELA 370</t>
+  </si>
+  <si>
+    <t>20054589</t>
+  </si>
+  <si>
+    <t>3SAPI KRIMER 490G</t>
+  </si>
+  <si>
+    <t>10036665</t>
+  </si>
+  <si>
+    <t>CARNATION KKM 365G</t>
+  </si>
+  <si>
+    <t>20105631</t>
+  </si>
+  <si>
+    <t>CARNATION KKM 405G</t>
+  </si>
+  <si>
+    <t>20101859</t>
+  </si>
+  <si>
+    <t>SUNBAY EVP.MILK 380G</t>
+  </si>
+  <si>
+    <t>20112906</t>
+  </si>
+  <si>
+    <t>T/SAPI SS EVAPORS500</t>
+  </si>
+  <si>
+    <t>20136510</t>
+  </si>
+  <si>
+    <t>MILO 3IN1 ACT-GO 400</t>
+  </si>
+  <si>
+    <t>20027850</t>
+  </si>
+  <si>
+    <t>ZEE SS VNL TWS 340 G</t>
+  </si>
+  <si>
+    <t>20027848</t>
+  </si>
+  <si>
+    <t>ZEE SS SWZ CHO 340 G</t>
+  </si>
+  <si>
+    <t>10033006</t>
+  </si>
+  <si>
+    <t>PRENAGEN HML CHO 180</t>
+  </si>
+  <si>
+    <t>20011063</t>
+  </si>
+  <si>
+    <t>PRENAGEN HML CHO 360</t>
+  </si>
+  <si>
+    <t>20033353</t>
+  </si>
+  <si>
+    <t>HILO/S HI-CAL CHO250</t>
+  </si>
+  <si>
+    <t>10000578</t>
+  </si>
+  <si>
+    <t>DIABETASOL VNL 170 G</t>
+  </si>
+  <si>
+    <t>20142907</t>
+  </si>
+  <si>
+    <t>MILKOW A/G 1 MDU 600</t>
+  </si>
+  <si>
+    <t>20142909</t>
+  </si>
+  <si>
+    <t>MILKOW A/G 1 VNL 600</t>
+  </si>
+  <si>
+    <t>20142910</t>
+  </si>
+  <si>
+    <t>MILKOW A/G 1 MDU 900</t>
+  </si>
+  <si>
+    <t>20142908</t>
+  </si>
+  <si>
+    <t>MILKOW A/G 1 VNL 900</t>
+  </si>
+  <si>
+    <t>20070110</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT1+ MDU700</t>
+  </si>
+  <si>
+    <t>20090042</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT1+ VAN700</t>
+  </si>
+  <si>
+    <t>20082394</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT3+ MDU700</t>
+  </si>
+  <si>
+    <t>20090437</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT3+ VAN700</t>
+  </si>
+  <si>
+    <t>20117983</t>
+  </si>
+  <si>
+    <t>VDORAN X5+ COK 700 G</t>
+  </si>
+  <si>
+    <t>20098371</t>
+  </si>
+  <si>
+    <t>VDORAN X3+ MDU 350 G</t>
+  </si>
+  <si>
+    <t>20098369</t>
+  </si>
+  <si>
+    <t>VDORAN X3+ VAN 350 G</t>
+  </si>
+  <si>
+    <t>20101825</t>
+  </si>
+  <si>
+    <t>VDRAN XMRT1+ MDU 900</t>
+  </si>
+  <si>
+    <t>20113346</t>
+  </si>
+  <si>
+    <t>VDRAN XMRT1+ VAN 900</t>
+  </si>
+  <si>
+    <t>20106381</t>
+  </si>
+  <si>
+    <t>VDRAN XMRT3+ MDU 900</t>
+  </si>
+  <si>
+    <t>20098370</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT1+ MDU325</t>
+  </si>
+  <si>
+    <t>20098368</t>
+  </si>
+  <si>
+    <t>VDORAN XMRT1+ VAN325</t>
+  </si>
+  <si>
+    <t>20138473</t>
+  </si>
+  <si>
+    <t>VDORAN BABY6-12 900G</t>
+  </si>
+  <si>
+    <t>20117981</t>
+  </si>
+  <si>
+    <t>VIDORAN XM3+ VNL900</t>
+  </si>
+  <si>
+    <t>20138474</t>
+  </si>
+  <si>
+    <t>VDRN XMRT5+ MDU 900G</t>
+  </si>
+  <si>
+    <t>20135200</t>
+  </si>
+  <si>
+    <t>VIDORAN BABY0-6 550G</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20129773</t>
+  </si>
+  <si>
+    <t>VDORAN BABY6-12 550G</t>
+  </si>
+  <si>
+    <t>20117985</t>
+  </si>
+  <si>
+    <t>VDORAN X5+ MDU 700 G</t>
+  </si>
+  <si>
+    <t>20142954</t>
+  </si>
+  <si>
+    <t>VDORAN X5+ VAN 700 G</t>
+  </si>
+  <si>
+    <t>20125788</t>
+  </si>
+  <si>
+    <t>HLTHYWY1+ SP MADU700</t>
+  </si>
+  <si>
+    <t>20032058</t>
+  </si>
+  <si>
+    <t>FF KENTAL MANIS 6X37</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>20013433</t>
+  </si>
+  <si>
+    <t>INDOMILK SKM PTH6X37</t>
+  </si>
+  <si>
+    <t>20087580</t>
+  </si>
+  <si>
+    <t>ENTRASOL GLD VAN560</t>
+  </si>
+  <si>
+    <t>10025373</t>
+  </si>
+  <si>
+    <t>ENTRSL GOLD VA 170 G</t>
+  </si>
+  <si>
+    <t>20021571</t>
+  </si>
+  <si>
+    <t>ANLENE GOLD VAN 560G</t>
+  </si>
+  <si>
+    <t>10020147</t>
+  </si>
+  <si>
+    <t>ANLENE GOLD CO 230 G</t>
+  </si>
+  <si>
+    <t>10008064</t>
+  </si>
+  <si>
+    <t>ANLENE GOLD OR 240 G</t>
+  </si>
+  <si>
+    <t>10012172</t>
+  </si>
+  <si>
+    <t>ANLENE GOLD VA 230 G</t>
+  </si>
+  <si>
+    <t>10003653</t>
+  </si>
+  <si>
+    <t>MRINAGA BMT1 LAC.390</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>20014399</t>
+  </si>
+  <si>
+    <t>MRINAGA CK3 VA 780 G</t>
+  </si>
+  <si>
+    <t>10005241</t>
+  </si>
+  <si>
+    <t>MORINAGA CM ORGN 190</t>
+  </si>
+  <si>
+    <t>10008314</t>
+  </si>
+  <si>
+    <t>MRINAGA CK VNL 190 G</t>
+  </si>
+  <si>
+    <t>10008316</t>
+  </si>
+  <si>
+    <t>MRINAGA CK MD 190 G</t>
+  </si>
+  <si>
+    <t>10010874</t>
+  </si>
+  <si>
+    <t>DNCOW1+ MDU BX 120 G</t>
+  </si>
+  <si>
+    <t>10005338</t>
+  </si>
+  <si>
+    <t>DNCOW FRTG BX 195 G</t>
+  </si>
+  <si>
+    <t>10026038</t>
+  </si>
+  <si>
+    <t>SGM EKSPL1+ MADU 150</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20040575</t>
+  </si>
+  <si>
+    <t>SGM EKSPL1+ VAN 150G</t>
+  </si>
+  <si>
+    <t>20056930</t>
+  </si>
+  <si>
+    <t>SGM EKSPL3+ MADU 150</t>
+  </si>
+  <si>
+    <t>20037098</t>
+  </si>
+  <si>
+    <t>SGM SOYA 1+ VANL 400</t>
+  </si>
+  <si>
+    <t>20040302</t>
+  </si>
+  <si>
+    <t>SGM EKSPL3+ MADU 350</t>
+  </si>
+  <si>
+    <t>20040301</t>
+  </si>
+  <si>
+    <t>SGM EKSPL3+ VAN 350G</t>
+  </si>
+  <si>
+    <t>10009494</t>
+  </si>
+  <si>
+    <t>DNCOW FORTIGRO 390 G</t>
+  </si>
+  <si>
+    <t>20040340</t>
+  </si>
+  <si>
+    <t>SGM ANANDA1 BOX 400G</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>20040312</t>
+  </si>
+  <si>
+    <t>SGM ANANDA2 BOX 400G</t>
+  </si>
+  <si>
+    <t>20040299</t>
+  </si>
+  <si>
+    <t>SGM EKSPL1+ MADU 350</t>
+  </si>
+  <si>
+    <t>20040300</t>
+  </si>
+  <si>
+    <t>SGM EKSPL1+ VAN 350G</t>
+  </si>
+  <si>
+    <t>20087025</t>
+  </si>
+  <si>
+    <t>SGM EKSPL3+ VAN 600G</t>
+  </si>
+  <si>
+    <t>20087024</t>
+  </si>
+  <si>
+    <t>SGM EKSPL3+ MADU 600</t>
+  </si>
+  <si>
+    <t>20047323</t>
+  </si>
+  <si>
+    <t>SGM ANANDA1 BOX 550G</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20047324</t>
+  </si>
+  <si>
+    <t>SGM ANANDA2 BOX 550G</t>
+  </si>
+  <si>
+    <t>20074147</t>
+  </si>
+  <si>
+    <t>SGM EKSPL1+ MD 600 G</t>
+  </si>
+  <si>
+    <t>20077508</t>
+  </si>
+  <si>
+    <t>SGM EKSPL1+ VN 600 G</t>
+  </si>
+  <si>
+    <t>20040294</t>
+  </si>
+  <si>
+    <t>SGM EKSPL1+ MADU 900</t>
+  </si>
+  <si>
+    <t>10005279</t>
+  </si>
+  <si>
+    <t>SGM ANANDA2 BOX 150G</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>20040293</t>
+  </si>
+  <si>
+    <t>SGM EKSPL1+ VAN 900G</t>
+  </si>
+  <si>
+    <t>20040296</t>
+  </si>
+  <si>
+    <t>SGM EKSPL3+ MADU 900</t>
+  </si>
+  <si>
+    <t>20040295</t>
+  </si>
+  <si>
+    <t>SGM EKSPL3+ VAN 900G</t>
+  </si>
+  <si>
+    <t>20066494</t>
+  </si>
+  <si>
+    <t>SGM EKSPL5+ MD 900 G</t>
+  </si>
+  <si>
+    <t>10005315</t>
+  </si>
+  <si>
+    <t>SGM ANANDA1 BOX 150G</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>20040297</t>
+  </si>
+  <si>
+    <t>SGM ANANDA1 BOX 1KG</t>
+  </si>
+  <si>
+    <t>20040298</t>
+  </si>
+  <si>
+    <t>SGM ANANDA2 BOX 1KG</t>
+  </si>
+  <si>
+    <t>20065379</t>
+  </si>
+  <si>
+    <t>SGM SOYA1+VNL  700 G</t>
+  </si>
+  <si>
+    <t>20071686</t>
+  </si>
+  <si>
+    <t>SGM SOYA1+MD  700 G</t>
+  </si>
+  <si>
+    <t>20005712</t>
+  </si>
+  <si>
+    <t>DNCOW 5+ VAN BOX 350</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>10009495</t>
+  </si>
+  <si>
+    <t>DNCOW FRTG F.C 390 G</t>
+  </si>
+  <si>
+    <t>10009493</t>
+  </si>
+  <si>
+    <t>DNCOW FRTG CKL 390 G</t>
+  </si>
+  <si>
+    <t>10006259</t>
+  </si>
+  <si>
+    <t>DANCOW FRTG 780 G</t>
+  </si>
+  <si>
+    <t>10006260</t>
+  </si>
+  <si>
+    <t>DNCOW FRGO CKT 780 G</t>
+  </si>
+  <si>
+    <t>10006258</t>
+  </si>
+  <si>
+    <t>DNCOW FRTG F.C 780 G</t>
+  </si>
+  <si>
+    <t>10006262</t>
+  </si>
+  <si>
+    <t>DNCOW1+ MDU BX 750 G</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>10015652</t>
+  </si>
+  <si>
+    <t>DNCOW1+ VAN BX 750 G</t>
+  </si>
+  <si>
+    <t>10013035</t>
+  </si>
+  <si>
+    <t>DNCOW3+ MDU BX 750 G</t>
+  </si>
+  <si>
+    <t>10015650</t>
+  </si>
+  <si>
+    <t>DNCOW3+ VAN BX 750 G</t>
+  </si>
+  <si>
+    <t>10023780</t>
+  </si>
+  <si>
+    <t>DNCOW5+ MDU BX 750 G</t>
+  </si>
+  <si>
+    <t>10009496</t>
+  </si>
+  <si>
+    <t>DNCOW1+ MDU BX 350 G</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>10015653</t>
+  </si>
+  <si>
+    <t>DNCOW1+ VAN BX 350 G</t>
+  </si>
+  <si>
+    <t>10012967</t>
+  </si>
+  <si>
+    <t>DNCOW3+ MDU BX 350 G</t>
+  </si>
+  <si>
+    <t>10015651</t>
+  </si>
+  <si>
+    <t>DNCOW3+ VAN BX 350 G</t>
+  </si>
+  <si>
+    <t>20017679</t>
+  </si>
+  <si>
+    <t>LACTOGEN PRO LANJ350</t>
+  </si>
+  <si>
+    <t>20113345</t>
+  </si>
+  <si>
+    <t>LCTGRW PRO1+VN 350 G</t>
+  </si>
+  <si>
+    <t>20035629</t>
+  </si>
+  <si>
+    <t>BEBELAC1+ VN B 350 G</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>20035633</t>
+  </si>
+  <si>
+    <t>BEBELAC3+ VNL BOX350</t>
+  </si>
+  <si>
+    <t>20035635</t>
+  </si>
+  <si>
+    <t>BEBELAC3+ MDU BOX350</t>
+  </si>
+  <si>
+    <t>10025848</t>
+  </si>
+  <si>
+    <t>NTRILON R 3 VN 400 G</t>
+  </si>
+  <si>
+    <t>20055287</t>
+  </si>
+  <si>
+    <t>LCTGRW PRO1+MD 350 G</t>
+  </si>
+  <si>
+    <t>20017965</t>
+  </si>
+  <si>
+    <t>LACTOGEN PRO FORM350</t>
+  </si>
+  <si>
+    <t>20142948</t>
+  </si>
+  <si>
+    <t>BEBELOVE 6-12BLN 775</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>20142950</t>
+  </si>
+  <si>
+    <t>BEBELAC 1+ VAN 775G</t>
+  </si>
+  <si>
+    <t>20142951</t>
+  </si>
+  <si>
+    <t>BEBELAC 1+ MADU 775</t>
+  </si>
+  <si>
+    <t>20142947</t>
+  </si>
+  <si>
+    <t>BEBELOVE  0-6BLN 775</t>
+  </si>
+  <si>
+    <t>20057224</t>
+  </si>
+  <si>
+    <t>BEBELOVE1 0-6 BOX175</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>20045528</t>
+  </si>
+  <si>
+    <t>BEBELOVE2 6-12BOX175</t>
+  </si>
+  <si>
+    <t>20043039</t>
+  </si>
+  <si>
+    <t>BEBELAC1+ MDU BOX175</t>
+  </si>
+  <si>
+    <t>20035626</t>
+  </si>
+  <si>
+    <t>BEBELOVE 1 BOX 350GR</t>
+  </si>
+  <si>
+    <t>20035627</t>
+  </si>
+  <si>
+    <t>BEBELOVE2 6-12BOX350</t>
+  </si>
+  <si>
+    <t>20035631</t>
+  </si>
+  <si>
+    <t>BEBELAC1+ MD B 350 G</t>
+  </si>
+  <si>
+    <t>20136285</t>
+  </si>
+  <si>
+    <t>BEBELOVE2 6-12BOX600</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>20122291</t>
+  </si>
+  <si>
+    <t>BEBELAC1+ M BX 600 G</t>
+  </si>
+  <si>
+    <t>20122288</t>
+  </si>
+  <si>
+    <t>BEBELAC1+ V BX 600 G</t>
+  </si>
+  <si>
+    <t>20069146</t>
+  </si>
+  <si>
+    <t>BEBELAC1+ MD BX 1 KG</t>
+  </si>
+  <si>
+    <t>20069147</t>
+  </si>
+  <si>
+    <t>BEBELAC1+ VN BX 1 KG</t>
+  </si>
+  <si>
     <t>20100805</t>
   </si>
   <si>
     <t>PRMNA PUDNG CHO 4X25</t>
   </si>
   <si>
-    <t>20067680</t>
-  </si>
-  <si>
-    <t>PRMNA PUDNG STRW 100</t>
-  </si>
-  <si>
-    <t>20113322</t>
-  </si>
-  <si>
-    <t>PROMINA PASTA M&amp;C 70</t>
-  </si>
-  <si>
-    <t>20126004</t>
-  </si>
-  <si>
-    <t>PROMINA PASTA CCS 60</t>
-  </si>
-  <si>
-    <t>20126003</t>
-  </si>
-  <si>
-    <t>PRMNA MI BT AYM KP75</t>
-  </si>
-  <si>
-    <t>10025325</t>
-  </si>
-  <si>
-    <t>PRMNA SUPMI AYM SY81</t>
-  </si>
-  <si>
-    <t>10025326</t>
-  </si>
-  <si>
-    <t>PRMN SUPMI DG&amp;SYR 84</t>
-  </si>
-  <si>
-    <t>20135120</t>
-  </si>
-  <si>
-    <t>PRMNA SFTCRN BUTER15</t>
-  </si>
-  <si>
-    <t>20094437</t>
-  </si>
-  <si>
-    <t>PROMINA CRUNCHIES 20</t>
-  </si>
-  <si>
-    <t>20129287</t>
-  </si>
-  <si>
-    <t>PRMINA CRN SEAWED 20</t>
-  </si>
-  <si>
-    <t>20129288</t>
-  </si>
-  <si>
-    <t>PRMINA CRN CHKN.BR20</t>
-  </si>
-  <si>
-    <t>20136087</t>
-  </si>
-  <si>
-    <t>PRMNA SFTCRN STRWB15</t>
-  </si>
-  <si>
-    <t>20141387</t>
-  </si>
-  <si>
-    <t>PROMINA MC CHO.AL 42</t>
-  </si>
-  <si>
-    <t>20141376</t>
-  </si>
-  <si>
-    <t>PROMINA MC BL.CHS 42</t>
-  </si>
-  <si>
-    <t>20133324</t>
-  </si>
-  <si>
-    <t>PRMINA CRCKR BRCLI20</t>
-  </si>
-  <si>
-    <t>20134695</t>
-  </si>
-  <si>
-    <t>PRMNA CRCKR BRRIES20</t>
-  </si>
-  <si>
-    <t>20077368</t>
-  </si>
-  <si>
-    <t>PRMINA PUFF BNANA 15</t>
-  </si>
-  <si>
-    <t>20077369</t>
-  </si>
-  <si>
-    <t>PRMINA PUFF BLUBR 15</t>
-  </si>
-  <si>
-    <t>20092042</t>
-  </si>
-  <si>
-    <t>PRMINA PUFF STRWAP15</t>
-  </si>
-  <si>
-    <t>20138373</t>
-  </si>
-  <si>
-    <t>PROMINA PUFF WGYU 15</t>
-  </si>
-  <si>
-    <t>20139421</t>
-  </si>
-  <si>
-    <t>PRMINA YGR MLT SRW 8</t>
-  </si>
-  <si>
-    <t>20139431</t>
-  </si>
-  <si>
-    <t>PRMINA YGR MLT MLK 8</t>
-  </si>
-  <si>
-    <t>20138655</t>
-  </si>
-  <si>
-    <t>MILNA PUFFS SWEED 13</t>
-  </si>
-  <si>
-    <t>20109115</t>
-  </si>
-  <si>
-    <t>MLNA PUFFS ORG BNN15</t>
-  </si>
-  <si>
-    <t>20103062</t>
-  </si>
-  <si>
-    <t>MLNA PUFFS ORG AMB15</t>
-  </si>
-  <si>
-    <t>20103061</t>
-  </si>
-  <si>
-    <t>MLNA PUFFS ORG CHS15</t>
-  </si>
-  <si>
-    <t>20027865</t>
-  </si>
-  <si>
-    <t>MILNA SUP AYM JG 100</t>
-  </si>
-  <si>
-    <t>20027867</t>
-  </si>
-  <si>
-    <t>MILNA ATI AYM BYM120</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>20122054</t>
-  </si>
-  <si>
-    <t>MLNA BBR SLMN CB 100</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>20137013</t>
-  </si>
-  <si>
-    <t>MILNA CRNCH CHSE 20G</t>
-  </si>
-  <si>
-    <t>20138656</t>
-  </si>
-  <si>
-    <t>MILNA CRN BERIES 20</t>
-  </si>
-  <si>
-    <t>20115159</t>
-  </si>
-  <si>
-    <t>MLNA RC.CRAC BNANA20</t>
-  </si>
-  <si>
-    <t>20115158</t>
-  </si>
-  <si>
-    <t>MLNA RC.CRACK SPC 20</t>
-  </si>
-  <si>
-    <t>20092863</t>
-  </si>
-  <si>
-    <t>YB BABY CRCK STRW 25</t>
-  </si>
-  <si>
-    <t>20080924</t>
-  </si>
-  <si>
-    <t>YB BABY CRACK BNN 25</t>
-  </si>
-  <si>
-    <t>20143371</t>
-  </si>
-  <si>
-    <t>MNDE BRMN CKS TMGO40</t>
-  </si>
-  <si>
-    <t>20143372</t>
-  </si>
-  <si>
-    <t>MNDE BRMN CKS BNNA40</t>
-  </si>
-  <si>
-    <t>20142228</t>
-  </si>
-  <si>
-    <t>CAP ENAK CHOCO 535G</t>
-  </si>
-  <si>
-    <t>20125783</t>
-  </si>
-  <si>
-    <t>CAP/ENAK KKM PTH 535</t>
-  </si>
-  <si>
-    <t>20140647</t>
-  </si>
-  <si>
-    <t>ENAK K/MNS COKLAT260</t>
-  </si>
-  <si>
-    <t>20140646</t>
-  </si>
-  <si>
-    <t>ENAK K/MNS PUTIH 260</t>
-  </si>
-  <si>
-    <t>20143301</t>
-  </si>
-  <si>
-    <t>INDMLK CRM MTCHA 260</t>
+    <t>999</t>
   </si>
   <si>
     <t>10005489</t>
@@ -511,766 +1285,10 @@
     <t>FF KENTAL MANIS 370G</t>
   </si>
   <si>
-    <t>10000255</t>
-  </si>
-  <si>
-    <t>FF GOLD SKM PTH 370G</t>
-  </si>
-  <si>
-    <t>20002313</t>
-  </si>
-  <si>
-    <t>FF KRM MNS OMELA 370</t>
-  </si>
-  <si>
-    <t>20054589</t>
-  </si>
-  <si>
-    <t>3SAPI KRIMER 490G</t>
-  </si>
-  <si>
-    <t>10036665</t>
-  </si>
-  <si>
-    <t>CARNATION KKM 365G</t>
-  </si>
-  <si>
-    <t>20105631</t>
-  </si>
-  <si>
-    <t>CARNATION KKM 405G</t>
-  </si>
-  <si>
-    <t>20101859</t>
-  </si>
-  <si>
-    <t>SUNBAY EVP.MILK 380G</t>
-  </si>
-  <si>
-    <t>20136510</t>
-  </si>
-  <si>
-    <t>MILO 3IN1 ACT-GO 400</t>
-  </si>
-  <si>
-    <t>20027850</t>
-  </si>
-  <si>
-    <t>ZEE SS VNL TWS 340 G</t>
-  </si>
-  <si>
-    <t>20027848</t>
-  </si>
-  <si>
-    <t>ZEE SS SWZ CHO 340 G</t>
-  </si>
-  <si>
-    <t>10033006</t>
-  </si>
-  <si>
-    <t>PRENAGEN HML CHO 180</t>
-  </si>
-  <si>
-    <t>20011063</t>
-  </si>
-  <si>
-    <t>PRENAGEN HML CHO 360</t>
-  </si>
-  <si>
-    <t>20033353</t>
-  </si>
-  <si>
-    <t>HILO/S HI-CAL CHO250</t>
-  </si>
-  <si>
-    <t>10000578</t>
-  </si>
-  <si>
-    <t>DIABETASOL VNL 170 G</t>
-  </si>
-  <si>
-    <t>20142907</t>
-  </si>
-  <si>
-    <t>MILKOW A/G 1 MDU 600</t>
-  </si>
-  <si>
-    <t>20142909</t>
-  </si>
-  <si>
-    <t>MILKOW A/G 1 VNL 600</t>
-  </si>
-  <si>
-    <t>20142910</t>
-  </si>
-  <si>
-    <t>MILKOW A/G 1 MDU 900</t>
-  </si>
-  <si>
-    <t>20142908</t>
-  </si>
-  <si>
-    <t>MILKOW A/G 1 VNL 900</t>
-  </si>
-  <si>
-    <t>20070110</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT1+ MDU700</t>
-  </si>
-  <si>
-    <t>20090042</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT1+ VAN700</t>
-  </si>
-  <si>
-    <t>20082394</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT3+ MDU700</t>
-  </si>
-  <si>
-    <t>20090437</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT3+ VAN700</t>
-  </si>
-  <si>
-    <t>20117983</t>
-  </si>
-  <si>
-    <t>VDORAN X5+ COK 700 G</t>
-  </si>
-  <si>
-    <t>20098371</t>
-  </si>
-  <si>
-    <t>VDORAN X3+ MDU 350 G</t>
-  </si>
-  <si>
-    <t>20098369</t>
-  </si>
-  <si>
-    <t>VDORAN X3+ VAN 350 G</t>
-  </si>
-  <si>
-    <t>20101825</t>
-  </si>
-  <si>
-    <t>VDRAN XMRT1+ MDU 900</t>
-  </si>
-  <si>
-    <t>20113346</t>
-  </si>
-  <si>
-    <t>VDRAN XMRT1+ VAN 900</t>
-  </si>
-  <si>
-    <t>20106381</t>
-  </si>
-  <si>
-    <t>VDRAN XMRT3+ MDU 900</t>
-  </si>
-  <si>
-    <t>20098370</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT1+ MDU325</t>
-  </si>
-  <si>
-    <t>20098368</t>
-  </si>
-  <si>
-    <t>VDORAN XMRT1+ VAN325</t>
-  </si>
-  <si>
-    <t>20138473</t>
-  </si>
-  <si>
-    <t>VDORAN BABY6-12 900G</t>
-  </si>
-  <si>
-    <t>20117981</t>
-  </si>
-  <si>
-    <t>VIDORAN XM3+ VNL900</t>
-  </si>
-  <si>
-    <t>20138474</t>
-  </si>
-  <si>
-    <t>VDRN XMRT5+ MDU 900G</t>
-  </si>
-  <si>
-    <t>20135200</t>
-  </si>
-  <si>
-    <t>VIDORAN BABY0-6 550G</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>20129773</t>
-  </si>
-  <si>
-    <t>VDORAN BABY6-12 550G</t>
-  </si>
-  <si>
-    <t>20117985</t>
-  </si>
-  <si>
-    <t>VDORAN X5+ MDU 700 G</t>
-  </si>
-  <si>
-    <t>20142954</t>
-  </si>
-  <si>
-    <t>VDORAN X5+ VAN 700 G</t>
-  </si>
-  <si>
-    <t>20125788</t>
-  </si>
-  <si>
-    <t>HLTHYWY1+ SP MADU700</t>
-  </si>
-  <si>
-    <t>20032058</t>
-  </si>
-  <si>
-    <t>FF KENTAL MANIS 6X37</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>20013433</t>
-  </si>
-  <si>
-    <t>INDOMILK SKM PTH6X37</t>
-  </si>
-  <si>
-    <t>20087580</t>
-  </si>
-  <si>
-    <t>ENTRASOL GLD VAN560</t>
-  </si>
-  <si>
-    <t>10025373</t>
-  </si>
-  <si>
-    <t>ENTRSL GOLD VA 170 G</t>
-  </si>
-  <si>
-    <t>20021571</t>
-  </si>
-  <si>
-    <t>ANLENE GOLD VAN 560G</t>
-  </si>
-  <si>
-    <t>10020147</t>
-  </si>
-  <si>
-    <t>ANLENE GOLD CO 230 G</t>
-  </si>
-  <si>
-    <t>10008064</t>
-  </si>
-  <si>
-    <t>ANLENE GOLD OR 240 G</t>
-  </si>
-  <si>
-    <t>10012172</t>
-  </si>
-  <si>
-    <t>ANLENE GOLD VA 230 G</t>
-  </si>
-  <si>
-    <t>10003653</t>
-  </si>
-  <si>
-    <t>MRINAGA BMT1 LAC.390</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>20014399</t>
-  </si>
-  <si>
-    <t>MRINAGA CK3 VA 780 G</t>
-  </si>
-  <si>
-    <t>10005241</t>
-  </si>
-  <si>
-    <t>MORINAGA CM ORGN 190</t>
-  </si>
-  <si>
-    <t>10008314</t>
-  </si>
-  <si>
-    <t>MRINAGA CK VNL 190 G</t>
-  </si>
-  <si>
-    <t>10008316</t>
-  </si>
-  <si>
-    <t>MRINAGA CK MD 190 G</t>
-  </si>
-  <si>
-    <t>10010874</t>
-  </si>
-  <si>
-    <t>DNCOW1+ MDU BX 120 G</t>
-  </si>
-  <si>
-    <t>10005338</t>
-  </si>
-  <si>
-    <t>DNCOW FRTG BX 195 G</t>
-  </si>
-  <si>
-    <t>10026038</t>
-  </si>
-  <si>
-    <t>SGM EKSPL1+ MADU 150</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20040575</t>
-  </si>
-  <si>
-    <t>SGM EKSPL1+ VAN 150G</t>
-  </si>
-  <si>
-    <t>20056930</t>
-  </si>
-  <si>
-    <t>SGM EKSPL3+ MADU 150</t>
-  </si>
-  <si>
-    <t>20037098</t>
-  </si>
-  <si>
-    <t>SGM SOYA 1+ VANL 400</t>
-  </si>
-  <si>
-    <t>20040302</t>
-  </si>
-  <si>
-    <t>SGM EKSPL3+ MADU 350</t>
-  </si>
-  <si>
-    <t>20040301</t>
-  </si>
-  <si>
-    <t>SGM EKSPL3+ VAN 350G</t>
-  </si>
-  <si>
-    <t>10009494</t>
-  </si>
-  <si>
-    <t>DNCOW FORTIGRO 390 G</t>
-  </si>
-  <si>
-    <t>20040340</t>
-  </si>
-  <si>
-    <t>SGM ANANDA1 BOX 400G</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>20040312</t>
-  </si>
-  <si>
-    <t>SGM ANANDA2 BOX 400G</t>
-  </si>
-  <si>
-    <t>20040299</t>
-  </si>
-  <si>
-    <t>SGM EKSPL1+ MADU 350</t>
-  </si>
-  <si>
-    <t>20040300</t>
-  </si>
-  <si>
-    <t>SGM EKSPL1+ VAN 350G</t>
-  </si>
-  <si>
-    <t>20087025</t>
-  </si>
-  <si>
-    <t>SGM EKSPL3+ VAN 600G</t>
-  </si>
-  <si>
-    <t>20087024</t>
-  </si>
-  <si>
-    <t>SGM EKSPL3+ MADU 600</t>
-  </si>
-  <si>
-    <t>20047323</t>
-  </si>
-  <si>
-    <t>SGM ANANDA1 BOX 550G</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20047324</t>
-  </si>
-  <si>
-    <t>SGM ANANDA2 BOX 550G</t>
-  </si>
-  <si>
-    <t>20074147</t>
-  </si>
-  <si>
-    <t>SGM EKSPL1+ MD 600 G</t>
-  </si>
-  <si>
-    <t>20077508</t>
-  </si>
-  <si>
-    <t>SGM EKSPL1+ VN 600 G</t>
-  </si>
-  <si>
-    <t>20040294</t>
-  </si>
-  <si>
-    <t>SGM EKSPL1+ MADU 900</t>
-  </si>
-  <si>
-    <t>10005279</t>
-  </si>
-  <si>
-    <t>SGM ANANDA2 BOX 150G</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>20040293</t>
-  </si>
-  <si>
-    <t>SGM EKSPL1+ VAN 900G</t>
-  </si>
-  <si>
-    <t>20040296</t>
-  </si>
-  <si>
-    <t>SGM EKSPL3+ MADU 900</t>
-  </si>
-  <si>
-    <t>20040295</t>
-  </si>
-  <si>
-    <t>SGM EKSPL3+ VAN 900G</t>
-  </si>
-  <si>
-    <t>20066494</t>
-  </si>
-  <si>
-    <t>SGM EKSPL5+ MD 900 G</t>
-  </si>
-  <si>
-    <t>10005315</t>
-  </si>
-  <si>
-    <t>SGM ANANDA1 BOX 150G</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>20040297</t>
-  </si>
-  <si>
-    <t>SGM ANANDA1 BOX 1KG</t>
-  </si>
-  <si>
-    <t>20040298</t>
-  </si>
-  <si>
-    <t>SGM ANANDA2 BOX 1KG</t>
-  </si>
-  <si>
-    <t>20065379</t>
-  </si>
-  <si>
-    <t>SGM SOYA1+VNL  700 G</t>
-  </si>
-  <si>
-    <t>20071686</t>
-  </si>
-  <si>
-    <t>SGM SOYA1+MD  700 G</t>
-  </si>
-  <si>
-    <t>20005712</t>
-  </si>
-  <si>
-    <t>DNCOW 5+ VAN BOX 350</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>10009495</t>
-  </si>
-  <si>
-    <t>DNCOW FRTG F.C 390 G</t>
-  </si>
-  <si>
-    <t>10009493</t>
-  </si>
-  <si>
-    <t>DNCOW FRTG CKL 390 G</t>
-  </si>
-  <si>
-    <t>10006259</t>
-  </si>
-  <si>
-    <t>DANCOW FRTG 780 G</t>
-  </si>
-  <si>
-    <t>10006260</t>
-  </si>
-  <si>
-    <t>DNCOW FRGO CKT 780 G</t>
-  </si>
-  <si>
-    <t>10006258</t>
-  </si>
-  <si>
-    <t>DNCOW FRTG F.C 780 G</t>
-  </si>
-  <si>
-    <t>10006262</t>
-  </si>
-  <si>
-    <t>DNCOW1+ MDU BX 750 G</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>10015652</t>
-  </si>
-  <si>
-    <t>DNCOW1+ VAN BX 750 G</t>
-  </si>
-  <si>
-    <t>10013035</t>
-  </si>
-  <si>
-    <t>DNCOW3+ MDU BX 750 G</t>
-  </si>
-  <si>
-    <t>10015650</t>
-  </si>
-  <si>
-    <t>DNCOW3+ VAN BX 750 G</t>
-  </si>
-  <si>
-    <t>10023780</t>
-  </si>
-  <si>
-    <t>DNCOW5+ MDU BX 750 G</t>
-  </si>
-  <si>
-    <t>10009496</t>
-  </si>
-  <si>
-    <t>DNCOW1+ MDU BX 350 G</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>10015653</t>
-  </si>
-  <si>
-    <t>DNCOW1+ VAN BX 350 G</t>
-  </si>
-  <si>
-    <t>10012967</t>
-  </si>
-  <si>
-    <t>DNCOW3+ MDU BX 350 G</t>
-  </si>
-  <si>
-    <t>10015651</t>
-  </si>
-  <si>
-    <t>DNCOW3+ VAN BX 350 G</t>
-  </si>
-  <si>
-    <t>20017679</t>
-  </si>
-  <si>
-    <t>LACTOGEN PRO LANJ350</t>
-  </si>
-  <si>
-    <t>20113345</t>
-  </si>
-  <si>
-    <t>LCTGRW PRO1+VN 350 G</t>
-  </si>
-  <si>
-    <t>20035629</t>
-  </si>
-  <si>
-    <t>BEBELAC1+ VN B 350 G</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>20035633</t>
-  </si>
-  <si>
-    <t>BEBELAC3+ VNL BOX350</t>
-  </si>
-  <si>
-    <t>20035635</t>
-  </si>
-  <si>
-    <t>BEBELAC3+ MDU BOX350</t>
-  </si>
-  <si>
-    <t>10025848</t>
-  </si>
-  <si>
-    <t>NTRILON R 3 VN 400 G</t>
-  </si>
-  <si>
-    <t>20055287</t>
-  </si>
-  <si>
-    <t>LCTGRW PRO1+MD 350 G</t>
-  </si>
-  <si>
-    <t>20017965</t>
-  </si>
-  <si>
-    <t>LACTOGEN PRO FORM350</t>
-  </si>
-  <si>
-    <t>20142948</t>
-  </si>
-  <si>
-    <t>BEBELOVE 6-12BLN 775</t>
-  </si>
-  <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>20142950</t>
-  </si>
-  <si>
-    <t>BEBELAC 1+ VAN 775G</t>
-  </si>
-  <si>
-    <t>20142951</t>
-  </si>
-  <si>
-    <t>BEBELAC 1+ MADU 775</t>
-  </si>
-  <si>
-    <t>20142947</t>
-  </si>
-  <si>
-    <t>BEBELOVE  0-6BLN 775</t>
-  </si>
-  <si>
-    <t>20057224</t>
-  </si>
-  <si>
-    <t>BEBELOVE1 0-6 BOX175</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>20045528</t>
-  </si>
-  <si>
-    <t>BEBELOVE2 6-12BOX175</t>
-  </si>
-  <si>
-    <t>20043039</t>
-  </si>
-  <si>
-    <t>BEBELAC1+ MDU BOX175</t>
-  </si>
-  <si>
-    <t>20035626</t>
-  </si>
-  <si>
-    <t>BEBELOVE 1 BOX 350GR</t>
-  </si>
-  <si>
-    <t>20035627</t>
-  </si>
-  <si>
-    <t>BEBELOVE2 6-12BOX350</t>
-  </si>
-  <si>
-    <t>20035631</t>
-  </si>
-  <si>
-    <t>BEBELAC1+ MD B 350 G</t>
-  </si>
-  <si>
-    <t>20136285</t>
-  </si>
-  <si>
-    <t>BEBELOVE2 6-12BOX600</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>20122291</t>
-  </si>
-  <si>
-    <t>BEBELAC1+ M BX 600 G</t>
-  </si>
-  <si>
-    <t>20122288</t>
-  </si>
-  <si>
-    <t>BEBELAC1+ V BX 600 G</t>
-  </si>
-  <si>
-    <t>20069146</t>
-  </si>
-  <si>
-    <t>BEBELAC1+ MD BX 1 KG</t>
-  </si>
-  <si>
-    <t>20069147</t>
-  </si>
-  <si>
-    <t>BEBELAC1+ VN BX 1 KG</t>
-  </si>
-  <si>
     <t>20139959</t>
   </si>
   <si>
     <t>PRMN SALMON LM 120G</t>
-  </si>
-  <si>
-    <t>999</t>
   </si>
   <si>
     <t>10000088</t>
@@ -1699,7 +1717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F199"/>
+  <dimension ref="A1:F202"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -2407,7 +2425,7 @@
         <v>15</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2427,7 +2445,7 @@
         <v>19</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2467,7 +2485,7 @@
         <v>26</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
@@ -2661,10 +2679,10 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F48" s="1" t="s">
         <v>16</v>
@@ -2684,7 +2702,7 @@
         <v>23</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F49" s="1" t="s">
         <v>16</v>
@@ -2704,7 +2722,7 @@
         <v>23</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F50" s="1" t="s">
         <v>16</v>
@@ -2724,7 +2742,7 @@
         <v>23</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>16</v>
@@ -2744,7 +2762,7 @@
         <v>23</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>16</v>
@@ -2764,7 +2782,7 @@
         <v>23</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>16</v>
@@ -2784,7 +2802,7 @@
         <v>23</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>16</v>
@@ -2804,7 +2822,7 @@
         <v>23</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>16</v>
@@ -2824,7 +2842,7 @@
         <v>23</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>16</v>
@@ -2844,7 +2862,7 @@
         <v>23</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>16</v>
@@ -2864,7 +2882,7 @@
         <v>23</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>16</v>
@@ -2884,7 +2902,7 @@
         <v>23</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>134</v>
+        <v>38</v>
       </c>
       <c r="F59" s="1" t="s">
         <v>16</v>
@@ -2892,10 +2910,10 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B60" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="C60" s="1" t="s">
         <v>3</v>
@@ -2904,7 +2922,7 @@
         <v>23</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F60" s="1" t="s">
         <v>16</v>
@@ -2912,19 +2930,19 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="C61" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="E61" s="1" t="s">
         <v>139</v>
-      </c>
-      <c r="C61" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F61" s="1" t="s">
         <v>16</v>
@@ -2944,7 +2962,7 @@
         <v>26</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>16</v>
@@ -2964,7 +2982,7 @@
         <v>26</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>16</v>
@@ -2984,7 +3002,7 @@
         <v>26</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>16</v>
@@ -3004,10 +3022,10 @@
         <v>26</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -3024,7 +3042,7 @@
         <v>26</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F66" s="1" t="s">
         <v>63</v>
@@ -3044,10 +3062,10 @@
         <v>26</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -3064,7 +3082,7 @@
         <v>26</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F68" s="1" t="s">
         <v>16</v>
@@ -3081,10 +3099,10 @@
         <v>3</v>
       </c>
       <c r="D69" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E69" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>16</v>
@@ -3104,7 +3122,7 @@
         <v>29</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>16</v>
@@ -3124,7 +3142,7 @@
         <v>29</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>16</v>
@@ -3144,7 +3162,7 @@
         <v>29</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>16</v>
@@ -3164,7 +3182,7 @@
         <v>29</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>16</v>
@@ -3184,10 +3202,10 @@
         <v>29</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
@@ -3204,7 +3222,7 @@
         <v>29</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>20</v>
@@ -3224,7 +3242,7 @@
         <v>29</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F76" s="1" t="s">
         <v>20</v>
@@ -3244,7 +3262,7 @@
         <v>29</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F77" s="1" t="s">
         <v>16</v>
@@ -3264,7 +3282,7 @@
         <v>29</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F78" s="1" t="s">
         <v>5</v>
@@ -3284,7 +3302,7 @@
         <v>29</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>134</v>
+        <v>38</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>16</v>
@@ -3304,7 +3322,7 @@
         <v>29</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F80" s="1" t="s">
         <v>63</v>
@@ -3321,13 +3339,13 @@
         <v>3</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>4</v>
+        <v>139</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -3344,10 +3362,10 @@
         <v>32</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -3364,7 +3382,7 @@
         <v>32</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>16</v>
@@ -3384,10 +3402,10 @@
         <v>32</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
@@ -3404,10 +3422,10 @@
         <v>32</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>12</v>
+        <v>63</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
@@ -3424,10 +3442,10 @@
         <v>32</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -3444,10 +3462,10 @@
         <v>32</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
@@ -3461,13 +3479,13 @@
         <v>3</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -3484,7 +3502,7 @@
         <v>35</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F89" s="1" t="s">
         <v>16</v>
@@ -3504,7 +3522,7 @@
         <v>35</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F90" s="1" t="s">
         <v>16</v>
@@ -3524,7 +3542,7 @@
         <v>35</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>16</v>
@@ -3541,13 +3559,13 @@
         <v>3</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -3564,7 +3582,7 @@
         <v>38</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>5</v>
@@ -3584,7 +3602,7 @@
         <v>38</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>5</v>
@@ -3604,7 +3622,7 @@
         <v>38</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>5</v>
@@ -3624,7 +3642,7 @@
         <v>38</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>5</v>
@@ -3641,10 +3659,10 @@
         <v>3</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>134</v>
+        <v>38</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F97" s="1" t="s">
         <v>5</v>
@@ -3661,13 +3679,13 @@
         <v>3</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -3681,13 +3699,13 @@
         <v>3</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -3701,10 +3719,10 @@
         <v>3</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F100" s="1" t="s">
         <v>5</v>
@@ -3721,10 +3739,10 @@
         <v>3</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>5</v>
@@ -3741,10 +3759,10 @@
         <v>3</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>5</v>
@@ -3761,13 +3779,13 @@
         <v>3</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>63</v>
+        <v>5</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -3781,13 +3799,13 @@
         <v>3</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>16</v>
+        <v>63</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
@@ -3801,13 +3819,13 @@
         <v>3</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -3821,13 +3839,13 @@
         <v>3</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -3841,30 +3859,30 @@
         <v>3</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>232</v>
+        <v>139</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>63</v>
+        <v>16</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="B108" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="B108" s="1" t="s">
+      <c r="C108" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="C108" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>232</v>
-      </c>
       <c r="E108" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>63</v>
@@ -3881,13 +3899,13 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
@@ -3901,13 +3919,13 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
@@ -3921,13 +3939,13 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
@@ -3941,33 +3959,33 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B113" s="1" t="s">
+      <c r="C113" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D113" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="C113" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>243</v>
-      </c>
       <c r="E113" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
@@ -3981,10 +3999,10 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>16</v>
@@ -4001,13 +4019,13 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
@@ -4021,10 +4039,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>12</v>
@@ -4041,10 +4059,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>12</v>
@@ -4061,10 +4079,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>12</v>
@@ -4081,10 +4099,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>12</v>
@@ -4101,10 +4119,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>12</v>
@@ -4112,19 +4130,19 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B121" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="C121" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D121" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="C121" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>260</v>
-      </c>
       <c r="E121" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>12</v>
@@ -4141,10 +4159,10 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>12</v>
@@ -4161,10 +4179,10 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F123" s="1" t="s">
         <v>12</v>
@@ -4181,10 +4199,10 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F124" s="1" t="s">
         <v>12</v>
@@ -4201,13 +4219,13 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -4221,10 +4239,10 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F126" s="1" t="s">
         <v>5</v>
@@ -4241,10 +4259,10 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>5</v>
@@ -4252,19 +4270,19 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="B128" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B128" s="1" t="s">
+      <c r="C128" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="C128" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>275</v>
-      </c>
       <c r="E128" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>5</v>
@@ -4281,10 +4299,10 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>5</v>
@@ -4301,10 +4319,10 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>5</v>
@@ -4321,10 +4339,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>5</v>
@@ -4341,10 +4359,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>5</v>
@@ -4361,10 +4379,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>5</v>
@@ -4381,10 +4399,10 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="F134" s="1" t="s">
         <v>5</v>
@@ -4392,19 +4410,19 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
+        <v>290</v>
+      </c>
+      <c r="B135" s="1" t="s">
         <v>291</v>
       </c>
-      <c r="B135" s="1" t="s">
+      <c r="C135" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D135" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="C135" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>290</v>
-      </c>
       <c r="E135" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>5</v>
@@ -4421,10 +4439,10 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>5</v>
@@ -4441,10 +4459,10 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F137" s="1" t="s">
         <v>5</v>
@@ -4461,10 +4479,10 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F138" s="1" t="s">
         <v>5</v>
@@ -4481,10 +4499,10 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>5</v>
@@ -4501,10 +4519,10 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F140" s="1" t="s">
         <v>5</v>
@@ -4512,19 +4530,19 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B141" s="1" t="s">
         <v>304</v>
       </c>
-      <c r="B141" s="1" t="s">
+      <c r="C141" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D141" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="C141" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>303</v>
-      </c>
       <c r="E141" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>5</v>
@@ -4541,10 +4559,10 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>5</v>
@@ -4561,10 +4579,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>5</v>
@@ -4581,10 +4599,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -4601,10 +4619,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -4612,19 +4630,19 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B146" s="1" t="s">
         <v>315</v>
       </c>
-      <c r="B146" s="1" t="s">
+      <c r="C146" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D146" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="C146" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>314</v>
-      </c>
       <c r="E146" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>5</v>
@@ -4641,10 +4659,10 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F147" s="1" t="s">
         <v>5</v>
@@ -4661,10 +4679,10 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F148" s="1" t="s">
         <v>5</v>
@@ -4681,13 +4699,13 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -4701,30 +4719,30 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="B151" s="1" t="s">
         <v>326</v>
       </c>
-      <c r="B151" s="1" t="s">
+      <c r="C151" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D151" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="C151" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>325</v>
-      </c>
       <c r="E151" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F151" s="1" t="s">
         <v>5</v>
@@ -4741,13 +4759,13 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -4761,13 +4779,13 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -4781,10 +4799,10 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F154" s="1" t="s">
         <v>5</v>
@@ -4801,10 +4819,10 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F155" s="1" t="s">
         <v>5</v>
@@ -4812,19 +4830,19 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="B156" s="1" t="s">
         <v>337</v>
       </c>
-      <c r="B156" s="1" t="s">
+      <c r="C156" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D156" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="C156" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D156" s="1" t="s">
-        <v>336</v>
-      </c>
       <c r="E156" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F156" s="1" t="s">
         <v>5</v>
@@ -4841,10 +4859,10 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -4861,10 +4879,10 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -4881,10 +4899,10 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -4901,10 +4919,10 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -4921,10 +4939,10 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>349</v>
+        <v>338</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>5</v>
@@ -4932,19 +4950,19 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="B162" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="B162" s="1" t="s">
+      <c r="C162" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D162" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="C162" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>349</v>
-      </c>
       <c r="E162" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>5</v>
@@ -4961,10 +4979,10 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>5</v>
@@ -4981,10 +4999,10 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F164" s="1" t="s">
         <v>5</v>
@@ -5001,10 +5019,10 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>5</v>
@@ -5021,10 +5039,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>5</v>
@@ -5032,19 +5050,19 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>361</v>
       </c>
-      <c r="B167" s="1" t="s">
+      <c r="C167" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D167" s="1" t="s">
         <v>362</v>
       </c>
-      <c r="C167" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D167" s="1" t="s">
-        <v>360</v>
-      </c>
       <c r="E167" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>5</v>
@@ -5061,10 +5079,10 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>5</v>
@@ -5081,10 +5099,10 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>5</v>
@@ -5101,10 +5119,10 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F170" s="1" t="s">
         <v>5</v>
@@ -5121,10 +5139,10 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F171" s="1" t="s">
         <v>5</v>
@@ -5141,10 +5159,10 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>373</v>
+        <v>362</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>5</v>
@@ -5152,19 +5170,19 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="B173" s="1" t="s">
         <v>374</v>
       </c>
-      <c r="B173" s="1" t="s">
+      <c r="C173" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D173" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="C173" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D173" s="1" t="s">
-        <v>373</v>
-      </c>
       <c r="E173" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>5</v>
@@ -5181,10 +5199,10 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>5</v>
@@ -5201,10 +5219,10 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>5</v>
@@ -5221,10 +5239,10 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>5</v>
@@ -5241,10 +5259,10 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F177" s="1" t="s">
         <v>5</v>
@@ -5261,30 +5279,30 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>386</v>
+        <v>375</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="B179" s="1" t="s">
         <v>387</v>
       </c>
-      <c r="B179" s="1" t="s">
+      <c r="C179" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D179" s="1" t="s">
         <v>388</v>
       </c>
-      <c r="C179" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>386</v>
-      </c>
       <c r="E179" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F179" s="1" t="s">
         <v>16</v>
@@ -5301,10 +5319,10 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>16</v>
@@ -5321,10 +5339,10 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>16</v>
@@ -5341,30 +5359,30 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>395</v>
+        <v>388</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="B183" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="B183" s="1" t="s">
+      <c r="C183" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D183" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="C183" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>395</v>
-      </c>
       <c r="E183" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F183" s="1" t="s">
         <v>5</v>
@@ -5381,10 +5399,10 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F184" s="1" t="s">
         <v>5</v>
@@ -5401,10 +5419,10 @@
         <v>3</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -5421,10 +5439,10 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F186" s="1" t="s">
         <v>5</v>
@@ -5441,10 +5459,10 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>5</v>
@@ -5461,10 +5479,10 @@
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>408</v>
+        <v>397</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>5</v>
@@ -5472,22 +5490,22 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="B189" s="1" t="s">
         <v>409</v>
       </c>
-      <c r="B189" s="1" t="s">
+      <c r="C189" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D189" s="1" t="s">
         <v>410</v>
       </c>
-      <c r="C189" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D189" s="1" t="s">
-        <v>408</v>
-      </c>
       <c r="E189" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -5501,10 +5519,10 @@
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>16</v>
@@ -5521,13 +5539,13 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -5541,10 +5559,10 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F192" s="1" t="s">
         <v>5</v>
@@ -5561,10 +5579,10 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>5</v>
@@ -5572,22 +5590,22 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="B194" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="B194" s="1" t="s">
+      <c r="C194" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D194" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="C194" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D194" s="1" t="s">
-        <v>419</v>
-      </c>
       <c r="E194" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -5601,10 +5619,10 @@
         <v>3</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>20</v>
@@ -5621,13 +5639,13 @@
         <v>3</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -5641,13 +5659,13 @@
         <v>3</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
@@ -5661,13 +5679,13 @@
         <v>3</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>325</v>
+        <v>26</v>
       </c>
       <c r="F198" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
@@ -5681,12 +5699,72 @@
         <v>3</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>336</v>
+        <v>32</v>
       </c>
       <c r="F199" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A200" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="B200" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C200" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D200" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="E200" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F200" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A201" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B201" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="C201" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D201" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="E201" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F201" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A202" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B202" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="C202" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D202" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="E202" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="F202" s="1" t="s">
         <v>20</v>
       </c>
     </row>
